--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="48">
   <si>
     <t>No.</t>
   </si>
@@ -35,25 +35,43 @@
     <t>평균</t>
   </si>
   <si>
+    <t>387.8</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
     <t>424.1</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>4.2</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
+    <t>351.4</t>
+  </si>
+  <si>
+    <t>775.5</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>7.8</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>03일</t>
   </si>
   <si>
     <t>04일</t>
@@ -448,16 +466,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="s" s="31">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s" s="32">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -465,19 +483,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="36">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="37">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -485,19 +503,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -505,19 +523,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -525,19 +543,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -545,19 +563,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -565,19 +583,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -585,19 +603,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -605,19 +623,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -625,19 +643,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -645,19 +663,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -665,19 +683,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -685,19 +703,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -705,19 +723,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -725,19 +743,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -745,19 +763,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -765,19 +783,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -785,19 +803,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -805,19 +823,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -825,19 +843,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -845,19 +863,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -865,19 +883,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -885,19 +903,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -905,19 +923,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -925,19 +943,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -945,19 +963,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -965,19 +983,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -985,19 +1003,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1005,19 +1023,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1025,19 +1043,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1045,19 +1063,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="52">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>387.8</t>
+    <t>367.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.9</t>
+    <t>3.7</t>
   </si>
   <si>
     <t>01일</t>
@@ -71,10 +71,22 @@
     <t>03일</t>
   </si>
   <si>
+    <t>326.8</t>
+  </si>
+  <si>
+    <t>1102.3</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>11.0</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>04일</t>
   </si>
   <si>
     <t>05일</t>
@@ -509,13 +521,13 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -523,19 +535,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -543,19 +555,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -563,19 +575,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -583,19 +595,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -603,19 +615,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -623,19 +635,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -643,19 +655,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -663,19 +675,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -683,19 +695,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -703,19 +715,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -723,19 +735,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -743,19 +755,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -763,19 +775,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -783,19 +795,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -803,19 +815,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -823,19 +835,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -843,19 +855,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -863,19 +875,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -883,19 +895,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -903,19 +915,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -923,19 +935,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -943,19 +955,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -963,19 +975,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -983,19 +995,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1003,19 +1015,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1023,19 +1035,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1043,19 +1055,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1063,19 +1075,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="56">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>367.4</t>
+    <t>384.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.7</t>
+    <t>3.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -86,10 +86,22 @@
     <t>04일</t>
   </si>
   <si>
+    <t>434.3</t>
+  </si>
+  <si>
+    <t>1536.6</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>15.4</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>05일</t>
   </si>
   <si>
     <t>06일</t>
@@ -541,13 +553,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -555,19 +567,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -575,19 +587,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -595,19 +607,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -615,19 +627,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -635,19 +647,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -655,19 +667,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -675,19 +687,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -695,19 +707,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -715,19 +727,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -735,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -755,19 +767,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -775,19 +787,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -795,19 +807,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -815,19 +827,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -835,19 +847,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -855,19 +867,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -875,19 +887,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -895,19 +907,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -915,19 +927,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -935,19 +947,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -955,19 +967,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -975,19 +987,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -995,19 +1007,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1015,19 +1027,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1035,19 +1047,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1055,19 +1067,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1075,19 +1087,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="60">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>384.1</t>
+    <t>344.3</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.8</t>
+    <t>3.4</t>
   </si>
   <si>
     <t>01일</t>
@@ -86,10 +86,10 @@
     <t>04일</t>
   </si>
   <si>
-    <t>434.3</t>
-  </si>
-  <si>
-    <t>1536.6</t>
+    <t>434.5</t>
+  </si>
+  <si>
+    <t>1536.8</t>
   </si>
   <si>
     <t>4.3</t>
@@ -101,10 +101,22 @@
     <t>05일</t>
   </si>
   <si>
+    <t>184.6</t>
+  </si>
+  <si>
+    <t>1721.4</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>17.2</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>06일</t>
   </si>
   <si>
     <t>07일</t>
@@ -573,13 +585,13 @@
         <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -587,19 +599,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -607,19 +619,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -627,19 +639,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -647,19 +659,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -667,19 +679,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -687,19 +699,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -707,19 +719,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -727,19 +739,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -747,19 +759,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -767,19 +779,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -787,19 +799,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -807,19 +819,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -827,19 +839,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -847,19 +859,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -867,19 +879,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -887,19 +899,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -907,19 +919,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -927,19 +939,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -947,19 +959,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -967,19 +979,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -987,19 +999,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1007,19 +1019,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1027,19 +1039,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1047,19 +1059,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1067,19 +1079,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1087,19 +1099,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="63">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>344.3</t>
+    <t>331.5</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.4</t>
+    <t>3.3</t>
   </si>
   <si>
     <t>01일</t>
@@ -77,9 +77,6 @@
     <t>1102.3</t>
   </si>
   <si>
-    <t>3.3</t>
-  </si>
-  <si>
     <t>11.0</t>
   </si>
   <si>
@@ -116,10 +113,22 @@
     <t>06일</t>
   </si>
   <si>
+    <t>267.7</t>
+  </si>
+  <si>
+    <t>1989.1</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>19.9</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>07일</t>
   </si>
   <si>
     <t>08일</t>
@@ -548,10 +557,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s" s="34">
         <v>21</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -559,19 +568,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>23</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>24</v>
       </c>
-      <c r="D6" t="s" s="37">
+      <c r="E6" t="s" s="38">
         <v>25</v>
       </c>
-      <c r="E6" t="s" s="38">
+      <c r="F6" t="s" s="39">
         <v>26</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -579,19 +588,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>28</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>29</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>30</v>
       </c>
-      <c r="E7" t="s" s="33">
+      <c r="F7" t="s" s="34">
         <v>31</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -599,19 +608,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>33</v>
-      </c>
-      <c r="C8" t="s" s="36">
-        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
         <v>34</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -619,19 +628,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -639,19 +648,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -659,19 +668,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -679,19 +688,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -699,19 +708,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -719,19 +728,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -739,19 +748,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -759,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -779,19 +788,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -799,19 +808,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -819,19 +828,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -839,19 +848,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -859,19 +868,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -879,19 +888,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -899,19 +908,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -919,19 +928,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -939,19 +948,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -959,19 +968,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -979,19 +988,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -999,19 +1008,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1019,19 +1028,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1039,19 +1048,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1059,19 +1068,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1079,19 +1088,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1099,19 +1108,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -35,48 +35,51 @@
     <t>평균</t>
   </si>
   <si>
-    <t>331.5</t>
+    <t>341.3</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>424.1</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>351.4</t>
+  </si>
+  <si>
+    <t>775.5</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>7.8</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>326.8</t>
+  </si>
+  <si>
+    <t>1102.3</t>
+  </si>
+  <si>
     <t>3.3</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>424.1</t>
-  </si>
-  <si>
-    <t>4.2</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>351.4</t>
-  </si>
-  <si>
-    <t>775.5</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>7.8</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>326.8</t>
-  </si>
-  <si>
-    <t>1102.3</t>
-  </si>
-  <si>
     <t>11.0</t>
   </si>
   <si>
@@ -128,10 +131,22 @@
     <t>07일</t>
   </si>
   <si>
+    <t>399.7</t>
+  </si>
+  <si>
+    <t>2388.8</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>23.9</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>08일</t>
   </si>
   <si>
     <t>09일</t>
@@ -557,10 +572,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -568,19 +583,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -588,19 +603,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -608,19 +623,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -628,19 +643,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -648,19 +663,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -668,19 +683,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -688,19 +703,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -708,19 +723,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -728,19 +743,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -748,19 +763,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -768,19 +783,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -788,19 +803,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -808,19 +823,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -828,19 +843,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -848,19 +863,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -868,19 +883,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -888,19 +903,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -908,19 +923,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -928,19 +943,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -948,19 +963,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -968,19 +983,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -988,19 +1003,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1008,19 +1023,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1028,19 +1043,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1048,19 +1063,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1068,19 +1083,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1088,19 +1103,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1108,19 +1123,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="72">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>341.3</t>
+    <t>310.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.4</t>
+    <t>3.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -146,10 +146,22 @@
     <t>08일</t>
   </si>
   <si>
+    <t>91.6</t>
+  </si>
+  <si>
+    <t>2480.4</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>24.8</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>09일</t>
   </si>
   <si>
     <t>10일</t>
@@ -669,13 +681,13 @@
         <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -683,19 +695,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -703,19 +715,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -723,19 +735,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -743,19 +755,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -763,19 +775,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -783,19 +795,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -803,19 +815,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -823,19 +835,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -843,19 +855,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -863,19 +875,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -883,19 +895,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -903,19 +915,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -923,19 +935,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -943,19 +955,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -963,19 +975,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -983,19 +995,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1003,19 +1015,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1023,19 +1035,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1043,19 +1055,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1063,19 +1075,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1083,19 +1095,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1103,19 +1115,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1123,19 +1135,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="76">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>310.0</t>
+    <t>286.3</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.1</t>
+    <t>2.9</t>
   </si>
   <si>
     <t>01일</t>
@@ -161,10 +161,22 @@
     <t>09일</t>
   </si>
   <si>
+    <t>96.2</t>
+  </si>
+  <si>
+    <t>2576.6</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>25.8</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>10일</t>
   </si>
   <si>
     <t>11일</t>
@@ -701,13 +713,13 @@
         <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -715,19 +727,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -735,19 +747,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -755,19 +767,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -775,19 +787,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -795,19 +807,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -815,19 +827,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -835,19 +847,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -855,19 +867,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -875,19 +887,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -895,19 +907,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -915,19 +927,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -935,19 +947,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -955,19 +967,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -975,19 +987,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -995,19 +1007,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1015,19 +1027,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1035,19 +1047,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1055,19 +1067,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1075,19 +1087,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1095,19 +1107,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1115,19 +1127,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1135,19 +1147,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="88">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>286.3</t>
+    <t>316.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>2.9</t>
+    <t>3.2</t>
   </si>
   <si>
     <t>01일</t>
@@ -176,16 +176,52 @@
     <t>10일</t>
   </si>
   <si>
+    <t>205.7</t>
+  </si>
+  <si>
+    <t>2782.3</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>27.8</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>487.5</t>
+  </si>
+  <si>
+    <t>3269.8</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>32.7</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
+    <t>522.2</t>
+  </si>
+  <si>
+    <t>3792.0</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>37.9</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>12일</t>
-  </si>
-  <si>
-    <t>13일</t>
   </si>
   <si>
     <t>14일</t>
@@ -733,13 +769,13 @@
         <v>54</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -747,19 +783,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -767,19 +803,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -787,19 +823,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -807,19 +843,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -827,19 +863,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -847,19 +883,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -867,19 +903,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -887,19 +923,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -907,19 +943,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -927,19 +963,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -947,19 +983,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -967,19 +1003,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -987,19 +1023,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1007,19 +1043,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1027,19 +1063,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1047,19 +1083,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1067,19 +1103,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1087,19 +1123,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1107,19 +1143,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1127,19 +1163,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1147,19 +1183,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>316.0</t>
+    <t>323.5</t>
   </si>
   <si>
     <t>-</t>
@@ -206,10 +206,10 @@
     <t>12일</t>
   </si>
   <si>
-    <t>522.2</t>
-  </si>
-  <si>
-    <t>3792.0</t>
+    <t>523.6</t>
+  </si>
+  <si>
+    <t>3793.4</t>
   </si>
   <si>
     <t>5.2</t>
@@ -221,10 +221,22 @@
     <t>13일</t>
   </si>
   <si>
+    <t>411.8</t>
+  </si>
+  <si>
+    <t>4205.2</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>42.1</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>14일</t>
   </si>
   <si>
     <t>15일</t>
@@ -829,13 +841,13 @@
         <v>69</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -843,19 +855,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -863,19 +875,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -883,19 +895,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -903,19 +915,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -923,19 +935,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -943,19 +955,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -963,19 +975,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -983,19 +995,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1003,19 +1015,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1023,19 +1035,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1043,19 +1055,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1063,19 +1075,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1083,19 +1095,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1103,19 +1115,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1123,19 +1135,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1143,19 +1155,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1163,19 +1175,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1183,19 +1195,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="95">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>323.5</t>
+    <t>319.6</t>
   </si>
   <si>
     <t>-</t>
@@ -236,10 +236,19 @@
     <t>14일</t>
   </si>
   <si>
+    <t>269.1</t>
+  </si>
+  <si>
+    <t>4474.3</t>
+  </si>
+  <si>
+    <t>44.7</t>
+  </si>
+  <si>
+    <t>15일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>15일</t>
   </si>
   <si>
     <t>16일</t>
@@ -861,13 +870,13 @@
         <v>74</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -875,19 +884,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -895,19 +904,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -915,19 +924,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -935,19 +944,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -955,19 +964,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -975,19 +984,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -995,19 +1004,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1015,19 +1024,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1035,19 +1044,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1055,19 +1064,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1075,19 +1084,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1095,19 +1104,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1115,19 +1124,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1135,19 +1144,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1155,19 +1164,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1175,19 +1184,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1195,19 +1204,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="99">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>319.6</t>
+    <t>316.7</t>
   </si>
   <si>
     <t>-</t>
@@ -248,10 +248,22 @@
     <t>15일</t>
   </si>
   <si>
+    <t>276.8</t>
+  </si>
+  <si>
+    <t>4751.1</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>47.5</t>
+  </si>
+  <si>
+    <t>16일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>16일</t>
   </si>
   <si>
     <t>17일</t>
@@ -890,13 +902,13 @@
         <v>78</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -904,19 +916,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -924,19 +936,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -944,19 +956,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -964,19 +976,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -984,19 +996,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1004,19 +1016,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1024,19 +1036,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1044,19 +1056,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1064,19 +1076,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1084,19 +1096,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1104,19 +1116,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1124,19 +1136,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1144,19 +1156,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1164,19 +1176,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1184,19 +1196,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1204,19 +1216,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="102">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>316.7</t>
+    <t>319.0</t>
   </si>
   <si>
     <t>-</t>
@@ -248,10 +248,10 @@
     <t>15일</t>
   </si>
   <si>
-    <t>276.8</t>
-  </si>
-  <si>
-    <t>4751.1</t>
+    <t>277.6</t>
+  </si>
+  <si>
+    <t>4751.9</t>
   </si>
   <si>
     <t>2.8</t>
@@ -263,10 +263,19 @@
     <t>16일</t>
   </si>
   <si>
+    <t>351.6</t>
+  </si>
+  <si>
+    <t>5103.5</t>
+  </si>
+  <si>
+    <t>51.0</t>
+  </si>
+  <si>
+    <t>17일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>17일</t>
   </si>
   <si>
     <t>18일</t>
@@ -922,13 +931,13 @@
         <v>83</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -936,19 +945,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -956,19 +965,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -976,19 +985,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -996,19 +1005,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1016,19 +1025,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1036,19 +1045,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1056,19 +1065,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1076,19 +1085,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1096,19 +1105,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1116,19 +1125,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1136,19 +1145,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1156,19 +1165,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1176,19 +1185,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1196,19 +1205,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1216,19 +1225,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="106">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>319.0</t>
+    <t>322.5</t>
   </si>
   <si>
     <t>-</t>
@@ -263,10 +263,10 @@
     <t>16일</t>
   </si>
   <si>
-    <t>351.6</t>
-  </si>
-  <si>
-    <t>5103.5</t>
+    <t>352.2</t>
+  </si>
+  <si>
+    <t>5104.1</t>
   </si>
   <si>
     <t>51.0</t>
@@ -275,10 +275,22 @@
     <t>17일</t>
   </si>
   <si>
+    <t>378.1</t>
+  </si>
+  <si>
+    <t>5482.2</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>54.8</t>
+  </si>
+  <si>
+    <t>18일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>18일</t>
   </si>
   <si>
     <t>19일</t>
@@ -951,13 +963,13 @@
         <v>87</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -965,19 +977,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -985,19 +997,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1005,19 +1017,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1025,19 +1037,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1045,19 +1057,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1065,19 +1077,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1085,19 +1097,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1105,19 +1117,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1125,19 +1137,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1145,19 +1157,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1165,19 +1177,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1185,19 +1197,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1205,19 +1217,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1225,19 +1237,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="110">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>322.5</t>
+    <t>311.2</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.2</t>
+    <t>3.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -275,10 +275,10 @@
     <t>17일</t>
   </si>
   <si>
-    <t>378.1</t>
-  </si>
-  <si>
-    <t>5482.2</t>
+    <t>378.5</t>
+  </si>
+  <si>
+    <t>5482.6</t>
   </si>
   <si>
     <t>3.8</t>
@@ -290,10 +290,22 @@
     <t>18일</t>
   </si>
   <si>
+    <t>118.7</t>
+  </si>
+  <si>
+    <t>5601.3</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>56.0</t>
+  </si>
+  <si>
+    <t>19일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>19일</t>
   </si>
   <si>
     <t>20일</t>
@@ -983,13 +995,13 @@
         <v>92</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -997,19 +1009,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1017,19 +1029,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1037,19 +1049,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1057,19 +1069,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1077,19 +1089,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1097,19 +1109,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1117,19 +1129,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1137,19 +1149,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1157,19 +1169,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1177,19 +1189,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1197,19 +1209,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1217,19 +1229,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1237,19 +1249,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>311.2</t>
+    <t>317.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.1</t>
+    <t>3.2</t>
   </si>
   <si>
     <t>01일</t>
@@ -290,10 +290,10 @@
     <t>18일</t>
   </si>
   <si>
-    <t>118.7</t>
-  </si>
-  <si>
-    <t>5601.3</t>
+    <t>120.2</t>
+  </si>
+  <si>
+    <t>5602.8</t>
   </si>
   <si>
     <t>1.2</t>
@@ -305,10 +305,22 @@
     <t>19일</t>
   </si>
   <si>
+    <t>437.6</t>
+  </si>
+  <si>
+    <t>6040.4</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>60.4</t>
+  </si>
+  <si>
+    <t>20일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>20일</t>
   </si>
   <si>
     <t>21일</t>
@@ -1015,13 +1027,13 @@
         <v>97</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1029,19 +1041,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1049,19 +1061,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1069,19 +1081,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1089,19 +1101,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1109,19 +1121,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1129,19 +1141,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1149,19 +1161,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1169,19 +1181,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1189,19 +1201,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1209,19 +1221,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1229,19 +1241,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1249,19 +1261,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="118">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>317.9</t>
+    <t>308.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.2</t>
+    <t>3.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -305,10 +305,10 @@
     <t>19일</t>
   </si>
   <si>
-    <t>437.6</t>
-  </si>
-  <si>
-    <t>6040.4</t>
+    <t>439.0</t>
+  </si>
+  <si>
+    <t>6041.8</t>
   </si>
   <si>
     <t>4.4</t>
@@ -320,10 +320,22 @@
     <t>20일</t>
   </si>
   <si>
+    <t>130.6</t>
+  </si>
+  <si>
+    <t>6172.4</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>61.7</t>
+  </si>
+  <si>
+    <t>21일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>21일</t>
   </si>
   <si>
     <t>22일</t>
@@ -1047,13 +1059,13 @@
         <v>102</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1061,19 +1073,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1081,19 +1093,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1101,19 +1113,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1121,19 +1133,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1141,19 +1153,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1161,19 +1173,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1181,19 +1193,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1201,19 +1213,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1221,19 +1233,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1241,19 +1253,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1261,19 +1273,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="121">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>308.6</t>
+    <t>298.8</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.1</t>
+    <t>3.0</t>
   </si>
   <si>
     <t>01일</t>
@@ -335,10 +335,19 @@
     <t>21일</t>
   </si>
   <si>
+    <t>103.4</t>
+  </si>
+  <si>
+    <t>6275.8</t>
+  </si>
+  <si>
+    <t>62.8</t>
+  </si>
+  <si>
+    <t>22일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>22일</t>
   </si>
   <si>
     <t>23일</t>
@@ -1079,13 +1088,13 @@
         <v>107</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1093,19 +1102,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1113,19 +1122,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1133,19 +1142,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1153,19 +1162,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1173,19 +1182,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1193,19 +1202,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1213,19 +1222,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1233,19 +1242,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1253,19 +1262,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1273,19 +1282,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="124">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>298.8</t>
+    <t>293.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.0</t>
+    <t>2.9</t>
   </si>
   <si>
     <t>01일</t>
@@ -347,10 +347,19 @@
     <t>22일</t>
   </si>
   <si>
+    <t>178.1</t>
+  </si>
+  <si>
+    <t>6453.9</t>
+  </si>
+  <si>
+    <t>64.5</t>
+  </si>
+  <si>
+    <t>23일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>23일</t>
   </si>
   <si>
     <t>24일</t>
@@ -1108,13 +1117,13 @@
         <v>111</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1122,19 +1131,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1142,19 +1151,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1162,19 +1171,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1182,19 +1191,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1202,19 +1211,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1222,19 +1231,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1242,19 +1251,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1262,19 +1271,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1282,19 +1291,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="128">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>293.4</t>
+    <t>290.7</t>
   </si>
   <si>
     <t>-</t>
@@ -347,10 +347,10 @@
     <t>22일</t>
   </si>
   <si>
-    <t>178.1</t>
-  </si>
-  <si>
-    <t>6453.9</t>
+    <t>178.2</t>
+  </si>
+  <si>
+    <t>6454.0</t>
   </si>
   <si>
     <t>64.5</t>
@@ -359,10 +359,22 @@
     <t>23일</t>
   </si>
   <si>
+    <t>231.6</t>
+  </si>
+  <si>
+    <t>6685.6</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>66.9</t>
+  </si>
+  <si>
+    <t>24일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>24일</t>
   </si>
   <si>
     <t>25일</t>
@@ -1137,13 +1149,13 @@
         <v>115</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1151,19 +1163,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1171,19 +1183,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1191,19 +1203,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1211,19 +1223,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1231,19 +1243,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1251,19 +1263,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1271,19 +1283,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1291,19 +1303,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="131">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>290.7</t>
+    <t>296.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>2.9</t>
+    <t>3.0</t>
   </si>
   <si>
     <t>01일</t>
@@ -374,10 +374,19 @@
     <t>24일</t>
   </si>
   <si>
+    <t>441.0</t>
+  </si>
+  <si>
+    <t>7126.6</t>
+  </si>
+  <si>
+    <t>71.3</t>
+  </si>
+  <si>
+    <t>25일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>25일</t>
   </si>
   <si>
     <t>26일</t>
@@ -1169,13 +1178,13 @@
         <v>120</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1183,19 +1192,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1203,19 +1212,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1223,19 +1232,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1243,19 +1252,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1263,19 +1272,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1283,19 +1292,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1303,19 +1312,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="134">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>296.9</t>
+    <t>302.5</t>
   </si>
   <si>
     <t>-</t>
@@ -374,10 +374,10 @@
     <t>24일</t>
   </si>
   <si>
-    <t>441.0</t>
-  </si>
-  <si>
-    <t>7126.6</t>
+    <t>441.2</t>
+  </si>
+  <si>
+    <t>7126.8</t>
   </si>
   <si>
     <t>71.3</t>
@@ -386,10 +386,19 @@
     <t>25일</t>
   </si>
   <si>
+    <t>436.3</t>
+  </si>
+  <si>
+    <t>7563.1</t>
+  </si>
+  <si>
+    <t>75.6</t>
+  </si>
+  <si>
+    <t>26일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>26일</t>
   </si>
   <si>
     <t>27일</t>
@@ -1198,13 +1207,13 @@
         <v>124</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1212,19 +1221,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1232,19 +1241,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1252,19 +1261,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1272,19 +1281,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1292,19 +1301,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1312,19 +1321,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="137">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>302.5</t>
+    <t>309.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.0</t>
+    <t>3.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -386,22 +386,31 @@
     <t>25일</t>
   </si>
   <si>
-    <t>436.3</t>
-  </si>
-  <si>
-    <t>7563.1</t>
-  </si>
-  <si>
-    <t>75.6</t>
+    <t>440.2</t>
+  </si>
+  <si>
+    <t>7567.0</t>
+  </si>
+  <si>
+    <t>75.7</t>
   </si>
   <si>
     <t>26일</t>
   </si>
   <si>
+    <t>486.2</t>
+  </si>
+  <si>
+    <t>8053.2</t>
+  </si>
+  <si>
+    <t>80.5</t>
+  </si>
+  <si>
+    <t>27일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>27일</t>
   </si>
   <si>
     <t>28일</t>
@@ -1227,13 +1236,13 @@
         <v>128</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1241,19 +1250,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1261,19 +1270,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1281,19 +1290,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1301,19 +1310,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1321,19 +1330,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="139">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>309.7</t>
+    <t>314.6</t>
   </si>
   <si>
     <t>-</t>
@@ -398,22 +398,28 @@
     <t>26일</t>
   </si>
   <si>
-    <t>486.2</t>
-  </si>
-  <si>
-    <t>8053.2</t>
-  </si>
-  <si>
-    <t>80.5</t>
+    <t>488.2</t>
+  </si>
+  <si>
+    <t>8055.2</t>
+  </si>
+  <si>
+    <t>80.6</t>
   </si>
   <si>
     <t>27일</t>
   </si>
   <si>
+    <t>8494.2</t>
+  </si>
+  <si>
+    <t>84.9</t>
+  </si>
+  <si>
+    <t>28일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>28일</t>
   </si>
   <si>
     <t>29일</t>
@@ -1253,16 +1259,16 @@
         <v>131</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s" s="32">
         <v>132</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1270,19 +1276,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1290,19 +1296,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1310,19 +1316,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1330,19 +1336,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="143">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>314.6</t>
+    <t>317.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.1</t>
+    <t>3.2</t>
   </si>
   <si>
     <t>01일</t>
@@ -419,10 +419,22 @@
     <t>28일</t>
   </si>
   <si>
+    <t>385.5</t>
+  </si>
+  <si>
+    <t>8879.7</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>88.8</t>
+  </si>
+  <si>
+    <t>29일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>29일</t>
   </si>
   <si>
     <t>30일</t>
@@ -1282,13 +1294,13 @@
         <v>135</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1296,19 +1308,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1316,19 +1328,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1336,19 +1348,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="147">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>317.1</t>
+    <t>321.7</t>
   </si>
   <si>
     <t>-</t>
@@ -434,10 +434,22 @@
     <t>29일</t>
   </si>
   <si>
+    <t>449.9</t>
+  </si>
+  <si>
+    <t>9329.6</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>93.3</t>
+  </si>
+  <si>
+    <t>30일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>30일</t>
   </si>
   <si>
     <t>31일</t>
@@ -1314,13 +1326,13 @@
         <v>140</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1328,19 +1340,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1348,19 +1360,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="150">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>321.7</t>
+    <t>324.1</t>
   </si>
   <si>
     <t>-</t>
@@ -449,10 +449,19 @@
     <t>30일</t>
   </si>
   <si>
+    <t>393.0</t>
+  </si>
+  <si>
+    <t>9722.6</t>
+  </si>
+  <si>
+    <t>97.2</t>
+  </si>
+  <si>
+    <t>31일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>31일</t>
   </si>
 </sst>
 </file>
@@ -1346,13 +1355,13 @@
         <v>145</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1360,19 +1369,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-07-01.xlsx
+++ b/past_data/site_8024/2026-07-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="151">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>324.1</t>
+    <t>327.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.2</t>
+    <t>3.3</t>
   </si>
   <si>
     <t>01일</t>
@@ -77,9 +77,6 @@
     <t>1102.3</t>
   </si>
   <si>
-    <t>3.3</t>
-  </si>
-  <si>
     <t>11.0</t>
   </si>
   <si>
@@ -449,10 +446,10 @@
     <t>30일</t>
   </si>
   <si>
-    <t>393.0</t>
-  </si>
-  <si>
-    <t>9722.6</t>
+    <t>393.1</t>
+  </si>
+  <si>
+    <t>9722.7</t>
   </si>
   <si>
     <t>97.2</t>
@@ -461,7 +458,13 @@
     <t>31일</t>
   </si>
   <si>
-    <t>0.0</t>
+    <t>443.1</t>
+  </si>
+  <si>
+    <t>10165.8</t>
+  </si>
+  <si>
+    <t>101.7</t>
   </si>
 </sst>
 </file>
@@ -818,10 +821,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s" s="34">
         <v>21</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -829,19 +832,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>23</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>24</v>
       </c>
-      <c r="D6" t="s" s="37">
+      <c r="E6" t="s" s="38">
         <v>25</v>
       </c>
-      <c r="E6" t="s" s="38">
+      <c r="F6" t="s" s="39">
         <v>26</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -849,19 +852,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>28</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>29</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>30</v>
       </c>
-      <c r="E7" t="s" s="33">
+      <c r="F7" t="s" s="34">
         <v>31</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -869,19 +872,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>33</v>
       </c>
-      <c r="C8" t="s" s="36">
+      <c r="D8" t="s" s="37">
         <v>34</v>
       </c>
-      <c r="D8" t="s" s="37">
+      <c r="E8" t="s" s="38">
         <v>35</v>
       </c>
-      <c r="E8" t="s" s="38">
+      <c r="F8" t="s" s="39">
         <v>36</v>
-      </c>
-      <c r="F8" t="s" s="39">
-        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -889,19 +892,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s" s="31">
         <v>38</v>
       </c>
-      <c r="C9" t="s" s="31">
+      <c r="D9" t="s" s="32">
         <v>39</v>
       </c>
-      <c r="D9" t="s" s="32">
+      <c r="E9" t="s" s="33">
         <v>40</v>
       </c>
-      <c r="E9" t="s" s="33">
+      <c r="F9" t="s" s="34">
         <v>41</v>
-      </c>
-      <c r="F9" t="s" s="34">
-        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -909,19 +912,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s" s="36">
         <v>43</v>
       </c>
-      <c r="C10" t="s" s="36">
+      <c r="D10" t="s" s="37">
         <v>44</v>
       </c>
-      <c r="D10" t="s" s="37">
+      <c r="E10" t="s" s="38">
         <v>45</v>
       </c>
-      <c r="E10" t="s" s="38">
+      <c r="F10" t="s" s="39">
         <v>46</v>
-      </c>
-      <c r="F10" t="s" s="39">
-        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -929,19 +932,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s" s="31">
         <v>48</v>
       </c>
-      <c r="C11" t="s" s="31">
+      <c r="D11" t="s" s="32">
         <v>49</v>
       </c>
-      <c r="D11" t="s" s="32">
+      <c r="E11" t="s" s="33">
         <v>50</v>
       </c>
-      <c r="E11" t="s" s="33">
+      <c r="F11" t="s" s="34">
         <v>51</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -949,19 +952,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>53</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>54</v>
       </c>
-      <c r="D12" t="s" s="37">
+      <c r="E12" t="s" s="38">
         <v>55</v>
       </c>
-      <c r="E12" t="s" s="38">
+      <c r="F12" t="s" s="39">
         <v>56</v>
-      </c>
-      <c r="F12" t="s" s="39">
-        <v>57</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -969,19 +972,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>58</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>59</v>
       </c>
-      <c r="D13" t="s" s="32">
+      <c r="E13" t="s" s="33">
         <v>60</v>
       </c>
-      <c r="E13" t="s" s="33">
+      <c r="F13" t="s" s="34">
         <v>61</v>
-      </c>
-      <c r="F13" t="s" s="34">
-        <v>62</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -989,19 +992,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>62</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>63</v>
       </c>
-      <c r="C14" t="s" s="36">
+      <c r="D14" t="s" s="37">
         <v>64</v>
       </c>
-      <c r="D14" t="s" s="37">
+      <c r="E14" t="s" s="38">
         <v>65</v>
       </c>
-      <c r="E14" t="s" s="38">
+      <c r="F14" t="s" s="39">
         <v>66</v>
-      </c>
-      <c r="F14" t="s" s="39">
-        <v>67</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -1009,19 +1012,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>68</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>69</v>
       </c>
-      <c r="D15" t="s" s="32">
+      <c r="E15" t="s" s="33">
         <v>70</v>
       </c>
-      <c r="E15" t="s" s="33">
+      <c r="F15" t="s" s="34">
         <v>71</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>72</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -1029,19 +1032,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>72</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>73</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>74</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
+        <v>35</v>
+      </c>
+      <c r="F16" t="s" s="39">
         <v>75</v>
-      </c>
-      <c r="E16" t="s" s="38">
-        <v>36</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>76</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -1049,19 +1052,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>77</v>
       </c>
-      <c r="C17" t="s" s="31">
+      <c r="D17" t="s" s="32">
         <v>78</v>
       </c>
-      <c r="D17" t="s" s="32">
+      <c r="E17" t="s" s="33">
         <v>79</v>
       </c>
-      <c r="E17" t="s" s="33">
+      <c r="F17" t="s" s="34">
         <v>80</v>
-      </c>
-      <c r="F17" t="s" s="34">
-        <v>81</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1069,19 +1072,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
+        <v>81</v>
+      </c>
+      <c r="C18" t="s" s="36">
         <v>82</v>
       </c>
-      <c r="C18" t="s" s="36">
+      <c r="D18" t="s" s="37">
         <v>83</v>
-      </c>
-      <c r="D18" t="s" s="37">
-        <v>84</v>
       </c>
       <c r="E18" t="s" s="38">
         <v>16</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1089,19 +1092,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s" s="31">
         <v>86</v>
       </c>
-      <c r="C19" t="s" s="31">
+      <c r="D19" t="s" s="32">
         <v>87</v>
       </c>
-      <c r="D19" t="s" s="32">
+      <c r="E19" t="s" s="33">
         <v>88</v>
       </c>
-      <c r="E19" t="s" s="33">
+      <c r="F19" t="s" s="34">
         <v>89</v>
-      </c>
-      <c r="F19" t="s" s="34">
-        <v>90</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1109,19 +1112,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
+        <v>90</v>
+      </c>
+      <c r="C20" t="s" s="36">
         <v>91</v>
       </c>
-      <c r="C20" t="s" s="36">
+      <c r="D20" t="s" s="37">
         <v>92</v>
       </c>
-      <c r="D20" t="s" s="37">
+      <c r="E20" t="s" s="38">
         <v>93</v>
       </c>
-      <c r="E20" t="s" s="38">
+      <c r="F20" t="s" s="39">
         <v>94</v>
-      </c>
-      <c r="F20" t="s" s="39">
-        <v>95</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1129,19 +1132,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>96</v>
       </c>
-      <c r="C21" t="s" s="31">
+      <c r="D21" t="s" s="32">
         <v>97</v>
       </c>
-      <c r="D21" t="s" s="32">
+      <c r="E21" t="s" s="33">
         <v>98</v>
       </c>
-      <c r="E21" t="s" s="33">
+      <c r="F21" t="s" s="34">
         <v>99</v>
-      </c>
-      <c r="F21" t="s" s="34">
-        <v>100</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1149,19 +1152,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
+        <v>100</v>
+      </c>
+      <c r="C22" t="s" s="36">
         <v>101</v>
       </c>
-      <c r="C22" t="s" s="36">
+      <c r="D22" t="s" s="37">
         <v>102</v>
       </c>
-      <c r="D22" t="s" s="37">
+      <c r="E22" t="s" s="38">
         <v>103</v>
       </c>
-      <c r="E22" t="s" s="38">
+      <c r="F22" t="s" s="39">
         <v>104</v>
-      </c>
-      <c r="F22" t="s" s="39">
-        <v>105</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1169,19 +1172,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
+        <v>105</v>
+      </c>
+      <c r="C23" t="s" s="31">
         <v>106</v>
       </c>
-      <c r="C23" t="s" s="31">
+      <c r="D23" t="s" s="32">
         <v>107</v>
       </c>
-      <c r="D23" t="s" s="32">
+      <c r="E23" t="s" s="33">
+        <v>50</v>
+      </c>
+      <c r="F23" t="s" s="34">
         <v>108</v>
-      </c>
-      <c r="E23" t="s" s="33">
-        <v>51</v>
-      </c>
-      <c r="F23" t="s" s="34">
-        <v>109</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1189,19 +1192,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s" s="36">
         <v>110</v>
       </c>
-      <c r="C24" t="s" s="36">
+      <c r="D24" t="s" s="37">
         <v>111</v>
       </c>
-      <c r="D24" t="s" s="37">
+      <c r="E24" t="s" s="38">
+        <v>30</v>
+      </c>
+      <c r="F24" t="s" s="39">
         <v>112</v>
-      </c>
-      <c r="E24" t="s" s="38">
-        <v>31</v>
-      </c>
-      <c r="F24" t="s" s="39">
-        <v>113</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1209,19 +1212,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
+        <v>113</v>
+      </c>
+      <c r="C25" t="s" s="31">
         <v>114</v>
       </c>
-      <c r="C25" t="s" s="31">
+      <c r="D25" t="s" s="32">
         <v>115</v>
       </c>
-      <c r="D25" t="s" s="32">
+      <c r="E25" t="s" s="33">
         <v>116</v>
       </c>
-      <c r="E25" t="s" s="33">
+      <c r="F25" t="s" s="34">
         <v>117</v>
-      </c>
-      <c r="F25" t="s" s="34">
-        <v>118</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1229,19 +1232,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
+        <v>118</v>
+      </c>
+      <c r="C26" t="s" s="36">
         <v>119</v>
       </c>
-      <c r="C26" t="s" s="36">
+      <c r="D26" t="s" s="37">
         <v>120</v>
       </c>
-      <c r="D26" t="s" s="37">
+      <c r="E26" t="s" s="38">
+        <v>98</v>
+      </c>
+      <c r="F26" t="s" s="39">
         <v>121</v>
-      </c>
-      <c r="E26" t="s" s="38">
-        <v>99</v>
-      </c>
-      <c r="F26" t="s" s="39">
-        <v>122</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1249,19 +1252,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
+        <v>122</v>
+      </c>
+      <c r="C27" t="s" s="31">
         <v>123</v>
       </c>
-      <c r="C27" t="s" s="31">
+      <c r="D27" t="s" s="32">
         <v>124</v>
       </c>
-      <c r="D27" t="s" s="32">
+      <c r="E27" t="s" s="33">
+        <v>98</v>
+      </c>
+      <c r="F27" t="s" s="34">
         <v>125</v>
-      </c>
-      <c r="E27" t="s" s="33">
-        <v>99</v>
-      </c>
-      <c r="F27" t="s" s="34">
-        <v>126</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1269,19 +1272,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
+        <v>126</v>
+      </c>
+      <c r="C28" t="s" s="36">
         <v>127</v>
       </c>
-      <c r="C28" t="s" s="36">
+      <c r="D28" t="s" s="37">
         <v>128</v>
       </c>
-      <c r="D28" t="s" s="37">
+      <c r="E28" t="s" s="38">
+        <v>60</v>
+      </c>
+      <c r="F28" t="s" s="39">
         <v>129</v>
-      </c>
-      <c r="E28" t="s" s="38">
-        <v>61</v>
-      </c>
-      <c r="F28" t="s" s="39">
-        <v>130</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1289,19 +1292,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
+        <v>130</v>
+      </c>
+      <c r="C29" t="s" s="31">
+        <v>96</v>
+      </c>
+      <c r="D29" t="s" s="32">
         <v>131</v>
       </c>
-      <c r="C29" t="s" s="31">
-        <v>97</v>
-      </c>
-      <c r="D29" t="s" s="32">
+      <c r="E29" t="s" s="33">
+        <v>98</v>
+      </c>
+      <c r="F29" t="s" s="34">
         <v>132</v>
-      </c>
-      <c r="E29" t="s" s="33">
-        <v>99</v>
-      </c>
-      <c r="F29" t="s" s="34">
-        <v>133</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1309,19 +1312,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
+        <v>133</v>
+      </c>
+      <c r="C30" t="s" s="36">
         <v>134</v>
       </c>
-      <c r="C30" t="s" s="36">
+      <c r="D30" t="s" s="37">
         <v>135</v>
       </c>
-      <c r="D30" t="s" s="37">
+      <c r="E30" t="s" s="38">
         <v>136</v>
       </c>
-      <c r="E30" t="s" s="38">
+      <c r="F30" t="s" s="39">
         <v>137</v>
-      </c>
-      <c r="F30" t="s" s="39">
-        <v>138</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1329,19 +1332,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
+        <v>138</v>
+      </c>
+      <c r="C31" t="s" s="31">
         <v>139</v>
       </c>
-      <c r="C31" t="s" s="31">
+      <c r="D31" t="s" s="32">
         <v>140</v>
       </c>
-      <c r="D31" t="s" s="32">
+      <c r="E31" t="s" s="33">
         <v>141</v>
       </c>
-      <c r="E31" t="s" s="33">
+      <c r="F31" t="s" s="34">
         <v>142</v>
-      </c>
-      <c r="F31" t="s" s="34">
-        <v>143</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1349,19 +1352,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
+        <v>143</v>
+      </c>
+      <c r="C32" t="s" s="36">
         <v>144</v>
       </c>
-      <c r="C32" t="s" s="36">
+      <c r="D32" t="s" s="37">
         <v>145</v>
       </c>
-      <c r="D32" t="s" s="37">
+      <c r="E32" t="s" s="38">
+        <v>136</v>
+      </c>
+      <c r="F32" t="s" s="39">
         <v>146</v>
-      </c>
-      <c r="E32" t="s" s="38">
-        <v>137</v>
-      </c>
-      <c r="F32" t="s" s="39">
-        <v>147</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1369,19 +1372,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
+        <v>147</v>
+      </c>
+      <c r="C33" t="s" s="31">
         <v>148</v>
-      </c>
-      <c r="C33" t="s" s="31">
-        <v>149</v>
       </c>
       <c r="D33" t="s" s="32">
         <v>149</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
